--- a/Quizbot/data/RESULT_TEXTS.xlsx
+++ b/Quizbot/data/RESULT_TEXTS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\++My Codes\Web Develop\Telegam_Bale Bot\Keramat_Quizbot2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\++My Codes\Web Develop\Telegam_Bale Bot\Keramat_Quizbot2\Quizbot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1525539F-27EE-4401-9DB4-ECFB1A64F0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB85FCB8-C931-429E-9E10-7727E4844249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,34 +57,42 @@
     <t>پرتابگر دمپایی</t>
   </si>
   <si>
-    <t xml:space="preserve">والد پشتیبان و حمایتگر — (والدگری به سبک برج مراقبت)
+    <t xml:space="preserve">والد پشتیبان اما با خطوط قرمز </t>
+  </si>
+  <si>
+    <t xml:space="preserve">والد بدون پشتیبانی و با کنترل </t>
+  </si>
+  <si>
+    <t>باغبان</t>
+  </si>
+  <si>
+    <t>دوربین مداربسته</t>
+  </si>
+  <si>
+    <t>🏧 والدگری به سبک خودپرداز
+شما از آن والدهایی هستید که دلتان نمی‌آید به بچه «نه» بگویید! 😄 هر وقت چیزی بخواهد، تا جای ممکن تلاش می‌کنید فراهمش کنید؛ از محبت گرفته تا امکانات و امتیازهای ویژه. پیش شما بچه احساس دوست‌داشتنی بودن می‌کند.
+فقط یک نکته... خودپرداز همیشه «پرداخت» می‌کند، اما قرار نیست به جای آدم تصمیم بگیرد! وقتی همه‌چیز خیلی راحت فراهم شود، ممکن است بچه تحمل ناکامی، صبر و مسئولیت‌پذیری را کمتر یاد بگیرد.
+✨ راهکار: گاهی هدیه را با مسئولیت همراه کنید و به جای «همین الان باشه»، بگویید: «بیا با هم برای رسیدن بهش برنامه بریزیم
+یادت باشد: فرزندت بیشتر از اینکه به یک خودپرداز نیاز داشته باشد، به یک راهنما نیاز دارد؛ کسی که هم محبت کند، هم گاهی با یک «نهِ» مهربان، او را برای زندگی آماده کند. 💛
+پیشنهاد ما به شما *مطالعه کتاب بلوغ اقای عین صاد* هستش   🌱</t>
+  </si>
+  <si>
+    <t>والد پشتیبان و حمایتگر — (والدگری به سبک برج مراقبت)
 شما همیشه حواست به بچه‌ات هست؛ انگار یک برج مراقبت ۲۴ ساعته داری که هیچ اتفاقی از چشمش دور نمی‌مونه! ❤️
 کنارت، بچه احساس امنیت می‌کنه و می‌دونه هر وقت گیر کرد، یکی هست که پشتش باشه.
 فقط گاهی این مراقبت آن‌قدر زیاد می‌شه که قبل از اینکه بچه خودش راه‌حل پیدا کنه، شما وارد عمل می‌شی! 😄 اینجوری ممکنه کم‌کم به جای اعتماد به خودش، بیشتر به کمک شما عادت کنه.
 ✨ راهکار: گاهی به جای نجات دادن، فقط کنار زمین بازی بایست. بذار خودش امتحان کنه، اشتباه کنه و اگر لازم شد، آن وقت کمکش کن.
 یادت باشه: بهترین برج مراقبت، همیشه هواپیما را هدایت نمی‌کند؛ فقط وقتی لازم باشد، راه را نشان می‌دهد. 🛫
-پیشنهاد ما به شما مطالعه کتاب نقش ازادی در تربیت شهید بهشتی هستش  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">والد پشتیبان اما با خطوط قرمز </t>
-  </si>
-  <si>
-    <t xml:space="preserve">والد بدون پشتیبانی و با کنترل </t>
-  </si>
-  <si>
-    <t>باغبان</t>
-  </si>
-  <si>
-    <t>دوربین مداربسته</t>
-  </si>
-  <si>
-    <t xml:space="preserve">والد پشتیبان اما با خطوط قرمز — (والدگری به سبک باغبان)
+پیشنهاد ما به شما *مطالعه کتاب نقش ازادی در تربیت شهید بهشتی* هستش  🌱</t>
+  </si>
+  <si>
+    <t>والد پشتیبان اما با خطوط قرمز — (والدگری به سبک باغبان)
 شما مثل یک باغبان دلسوزی؛ به بچه‌ات آب می‌دی، نور می‌دی، مراقبشی و همزمان دور باغچه هم یک حصار محکم کشیدی تا از آسیب‌ها دور بمونه. 🌿❤️
 بچه کنار شما هم عشق رو تجربه می‌کنه، هم می‌دونه قانون یعنی قانون!
 فقط گاهی این حصار انقدر بلند می‌شه که حتی نسیم تجربه هم به داخل نمی‌رسه! 😄 ممکنه بچه به جای اینکه یاد بگیره خودش تصمیم بگیره، همیشه منتظر باشه ببیند حصار اجازه می‌دهد یا نه.
 ✨ راهکار: هر از گاهی یک «درِ کوچک» روی حصار باز کن. اجازه بده بچه در موقعیت‌های کم‌خطر، انتخاب کند، اشتباه کند و از تجربه‌های خودش یاد بگیرد.
 یادت باشد: باغبان خوب فقط از گیاه محافظت نمی‌کند؛ کمک می‌کند ریشه‌هایش آن‌قدر قوی شوند که روزی بیرون از حصار هم دوام بیاورند. 🌳
-پیشنهاد ما به شما مطالعه کتاب تفکر تعلق اقای حائری شیرازی هستش  </t>
+پیشنهاد ما به شما *مطالعه کتاب تفکر تعلق اقای حائری شیرازی* هستش  🌱</t>
   </si>
   <si>
     <t>📹 والدگری به سبک دوربین مداربسته
@@ -93,15 +101,7 @@
 ✨ راهکار: قبل از اینکه بپرسید «چرا این کار را کردی؟»، گاهی بپرسید «حالت چطور بود که این اتفاق افتاد؟»
 یادت باشد: بهترین امنیت، از ترسِ دیده شدن نمی‌آید؛ از احساسِ دیده شدن و درک شدن می‌آید. 
 📹🤝
-پیشنهاد ما به شما مطالعه من دیگر ما اقای عباسی ولدی هستش  🌱</t>
-  </si>
-  <si>
-    <t>🏧 والدگری به سبک خودپرداز
-شما از آن والدهایی هستید که دلتان نمی‌آید به بچه «نه» بگویید! 😄 هر وقت چیزی بخواهد، تا جای ممکن تلاش می‌کنید فراهمش کنید؛ از محبت گرفته تا امکانات و امتیازهای ویژه. پیش شما بچه احساس دوست‌داشتنی بودن می‌کند.
-فقط یک نکته... خودپرداز همیشه «پرداخت» می‌کند، اما قرار نیست به جای آدم تصمیم بگیرد! وقتی همه‌چیز خیلی راحت فراهم شود، ممکن است بچه تحمل ناکامی، صبر و مسئولیت‌پذیری را کمتر یاد بگیرد.
-✨ راهکار: گاهی هدیه را با مسئولیت همراه کنید و به جای «همین الان باشه»، بگویید: «بیا با هم برای رسیدن بهش برنامه بریزیم
-یادت باشد: فرزندت بیشتر از اینکه به یک خودپرداز نیاز داشته باشد، به یک راهنما نیاز دارد؛ کسی که هم محبت کند، هم گاهی با یک «نهِ» مهربان، او را برای زندگی آماده کند. 💛
-پیشنهاد ما به شما بلوغ اقای عین صاد هستش   🌱</t>
+پیشنهاد ما به شما *مطالعه من دیگر ما اقای عباسی ولدی* هستش  🌱</t>
   </si>
   <si>
     <t>🩴 والدگری با پرتاب دمپایی
@@ -109,7 +109,7 @@
 فقط یک مشکل کوچولو... وقتی ترس جای گفت‌وگو را بگیرد، بچه بیشتر یاد می‌گیرد از شما فاصله بگیرد تا اینکه اشتباهاتش را با شما در میان بگذارد.
 ✨ راهکار: قبل از واکنش، فقط ۱۰ ثانیه مکث کنید. خیلی وقت‌ها یک نفس عمیق، بیشتر از یک داد بلند اثر دارد.
 یادت باشد: دمپایی شاید چند قدم بچه را متوقف کند، اما آرامش و احترام، تا آخر مسیر همراهش می‌ماند. ❤️🩴
-پیشنهاد ما به شما مطالعه کتاب تربیت چه چیز نیست آقای عبدالعظیم کریمی هستش  🌱</t>
+پیشنهاد ما به شما *مطالعه کتاب تربیت چه چیز نیست آقای عبدالعظیم کریمی* هستش  🌱</t>
   </si>
 </sst>
 </file>
@@ -497,7 +497,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="172.8" x14ac:dyDescent="0.55000000000000004">
@@ -505,13 +505,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="187.2" x14ac:dyDescent="0.55000000000000004">
@@ -519,13 +519,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2" x14ac:dyDescent="0.55000000000000004">
@@ -539,7 +539,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="172.8" x14ac:dyDescent="0.55000000000000004">
